--- a/static/data/exports/Retro_PY_AE_2016.xlsx
+++ b/static/data/exports/Retro_PY_AE_2016.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -576,6 +576,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>44</v>
+      </c>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
@@ -638,6 +651,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>53</v>
+      </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
@@ -700,6 +726,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>36</v>
+      </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
@@ -762,6 +801,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>40</v>
+      </c>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
@@ -824,6 +876,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>38</v>
+      </c>
       <c r="Q6" t="b">
         <v>0</v>
       </c>
@@ -948,6 +1013,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>51</v>
+      </c>
       <c r="Q8" t="b">
         <v>0</v>
       </c>
@@ -1010,6 +1088,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>31</v>
+      </c>
       <c r="Q9" t="b">
         <v>0</v>
       </c>
@@ -1072,6 +1163,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>41</v>
+      </c>
       <c r="Q10" t="b">
         <v>0</v>
       </c>
@@ -1134,6 +1238,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>25</v>
+      </c>
       <c r="Q11" t="b">
         <v>0</v>
       </c>
@@ -1196,8 +1313,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>36</v>
+      </c>
       <c r="Q12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>26</v>
@@ -1258,6 +1388,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>40</v>
+      </c>
       <c r="Q13" t="b">
         <v>0</v>
       </c>
@@ -1320,6 +1463,19 @@
           <t>AgIMK</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>29</v>
+      </c>
       <c r="Q14" t="b">
         <v>0</v>
       </c>
@@ -1382,6 +1538,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>34</v>
+      </c>
       <c r="Q15" t="b">
         <v>0</v>
       </c>
@@ -1444,6 +1613,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>48</v>
+      </c>
       <c r="Q16" t="b">
         <v>0</v>
       </c>
@@ -1506,6 +1688,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>49</v>
+      </c>
       <c r="Q17" t="b">
         <v>0</v>
       </c>
@@ -1568,6 +1763,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>69</v>
+      </c>
       <c r="Q18" t="b">
         <v>0</v>
       </c>
@@ -1692,6 +1900,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>42</v>
+      </c>
       <c r="Q20" t="b">
         <v>0</v>
       </c>
@@ -1754,6 +1975,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>48</v>
+      </c>
       <c r="Q21" t="b">
         <v>0</v>
       </c>
@@ -1816,6 +2050,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>63</v>
+      </c>
       <c r="Q22" t="b">
         <v>0</v>
       </c>
@@ -1878,6 +2125,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>37</v>
+      </c>
       <c r="Q23" t="b">
         <v>0</v>
       </c>
@@ -1940,6 +2200,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>55</v>
+      </c>
       <c r="Q24" t="b">
         <v>0</v>
       </c>
@@ -2002,6 +2275,19 @@
           <t>AgIMK</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>29</v>
+      </c>
       <c r="Q25" t="b">
         <v>0</v>
       </c>
@@ -2064,6 +2350,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>30</v>
+      </c>
       <c r="Q26" t="b">
         <v>0</v>
       </c>
@@ -2126,6 +2425,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>51</v>
+      </c>
       <c r="Q27" t="b">
         <v>0</v>
       </c>
@@ -2188,6 +2500,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>43</v>
+      </c>
       <c r="Q28" t="b">
         <v>0</v>
       </c>
@@ -2250,6 +2575,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>52</v>
+      </c>
       <c r="Q29" t="b">
         <v>0</v>
       </c>
@@ -2312,6 +2650,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>40</v>
+      </c>
       <c r="Q30" t="b">
         <v>0</v>
       </c>
@@ -2374,6 +2725,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>60</v>
+      </c>
       <c r="Q31" t="b">
         <v>0</v>
       </c>
@@ -2436,6 +2800,19 @@
           <t>VCK</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>56</v>
+      </c>
       <c r="Q32" t="b">
         <v>0</v>
       </c>
@@ -2560,6 +2937,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>43</v>
+      </c>
       <c r="Q34" t="b">
         <v>0</v>
       </c>
@@ -2622,6 +3012,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>43</v>
+      </c>
       <c r="Q35" t="b">
         <v>0</v>
       </c>
@@ -2684,6 +3087,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>41</v>
+      </c>
       <c r="Q36" t="b">
         <v>0</v>
       </c>
@@ -2746,6 +3162,19 @@
           <t>AgIMK</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>40</v>
+      </c>
       <c r="Q37" t="b">
         <v>0</v>
       </c>
@@ -2808,6 +3237,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>29</v>
+      </c>
       <c r="Q38" t="b">
         <v>0</v>
       </c>
@@ -2870,6 +3312,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>50</v>
+      </c>
       <c r="Q39" t="b">
         <v>0</v>
       </c>
@@ -2932,6 +3387,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>45</v>
+      </c>
       <c r="Q40" t="b">
         <v>0</v>
       </c>
@@ -2994,6 +3462,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>66</v>
+      </c>
       <c r="Q41" t="b">
         <v>0</v>
       </c>
@@ -3118,6 +3599,19 @@
           <t>MDMK</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>40</v>
+      </c>
       <c r="Q43" t="b">
         <v>0</v>
       </c>
@@ -3180,6 +3674,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>46</v>
+      </c>
       <c r="Q44" t="b">
         <v>0</v>
       </c>
@@ -3242,6 +3749,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>40</v>
+      </c>
       <c r="Q45" t="b">
         <v>0</v>
       </c>
@@ -3304,6 +3824,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>34</v>
+      </c>
       <c r="Q46" t="b">
         <v>0</v>
       </c>
@@ -3366,6 +3899,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>51</v>
+      </c>
       <c r="Q47" t="b">
         <v>0</v>
       </c>
@@ -3428,6 +3974,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>33</v>
+      </c>
       <c r="Q48" t="b">
         <v>0</v>
       </c>
@@ -3490,6 +4049,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>44</v>
+      </c>
       <c r="Q49" t="b">
         <v>0</v>
       </c>
@@ -3552,6 +4124,19 @@
           <t>CPI(ML)(L)</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>49</v>
+      </c>
       <c r="Q50" t="b">
         <v>0</v>
       </c>
@@ -3614,6 +4199,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>36</v>
+      </c>
       <c r="Q51" t="b">
         <v>0</v>
       </c>
@@ -3676,6 +4274,19 @@
           <t>AgIMK</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>34</v>
+      </c>
       <c r="Q52" t="b">
         <v>0</v>
       </c>
@@ -3738,6 +4349,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>43</v>
+      </c>
       <c r="Q53" t="b">
         <v>0</v>
       </c>
@@ -3800,6 +4424,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>47</v>
+      </c>
       <c r="Q54" t="b">
         <v>1</v>
       </c>
@@ -3862,6 +4499,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>63</v>
+      </c>
       <c r="Q55" t="b">
         <v>0</v>
       </c>
@@ -3924,6 +4574,19 @@
           <t>VCK</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>36</v>
+      </c>
       <c r="Q56" t="b">
         <v>0</v>
       </c>
@@ -3986,6 +4649,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>53</v>
+      </c>
       <c r="Q57" t="b">
         <v>0</v>
       </c>
@@ -4110,6 +4786,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>41</v>
+      </c>
       <c r="Q59" t="b">
         <v>0</v>
       </c>
@@ -4172,6 +4861,19 @@
           <t>SDPI</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>35</v>
+      </c>
       <c r="Q60" t="b">
         <v>0</v>
       </c>
@@ -4234,6 +4936,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>38</v>
+      </c>
       <c r="Q61" t="b">
         <v>0</v>
       </c>
@@ -4296,6 +5011,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>45</v>
+      </c>
       <c r="Q62" t="b">
         <v>0</v>
       </c>
@@ -4358,6 +5086,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>34</v>
+      </c>
       <c r="Q63" t="b">
         <v>0</v>
       </c>
@@ -4420,6 +5161,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>30</v>
+      </c>
       <c r="Q64" t="b">
         <v>0</v>
       </c>
@@ -4482,6 +5236,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>36</v>
+      </c>
       <c r="Q65" t="b">
         <v>0</v>
       </c>
@@ -4544,6 +5311,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>40</v>
+      </c>
       <c r="Q66" t="b">
         <v>0</v>
       </c>
@@ -4606,6 +5386,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>40</v>
+      </c>
       <c r="Q67" t="b">
         <v>0</v>
       </c>
@@ -4668,6 +5461,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>51</v>
+      </c>
       <c r="Q68" t="b">
         <v>0</v>
       </c>
@@ -4730,6 +5536,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>54</v>
+      </c>
       <c r="Q69" t="b">
         <v>0</v>
       </c>
@@ -4792,6 +5611,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>55</v>
+      </c>
       <c r="Q70" t="b">
         <v>0</v>
       </c>
@@ -4854,6 +5686,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>51</v>
+      </c>
       <c r="Q71" t="b">
         <v>0</v>
       </c>
@@ -4916,6 +5761,19 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>49</v>
+      </c>
       <c r="Q72" t="b">
         <v>0</v>
       </c>
@@ -4978,6 +5836,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>38</v>
+      </c>
       <c r="Q73" t="b">
         <v>0</v>
       </c>
@@ -5102,6 +5973,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>64</v>
+      </c>
       <c r="Q75" t="b">
         <v>0</v>
       </c>
@@ -5164,6 +6048,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>31</v>
+      </c>
       <c r="Q76" t="b">
         <v>0</v>
       </c>
@@ -5226,6 +6123,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>52</v>
+      </c>
       <c r="Q77" t="b">
         <v>0</v>
       </c>
@@ -5288,6 +6198,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>31</v>
+      </c>
       <c r="Q78" t="b">
         <v>0</v>
       </c>
@@ -5350,8 +6273,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>45</v>
+      </c>
       <c r="Q79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
         <v>26</v>
@@ -5412,6 +6348,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>42</v>
+      </c>
       <c r="Q80" t="b">
         <v>0</v>
       </c>
@@ -5474,8 +6423,21 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>42</v>
+      </c>
       <c r="Q81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
         <v>26</v>
@@ -5536,6 +6498,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>29</v>
+      </c>
       <c r="Q82" t="b">
         <v>0</v>
       </c>
@@ -5598,6 +6573,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>42</v>
+      </c>
       <c r="Q83" t="b">
         <v>0</v>
       </c>
@@ -5660,6 +6648,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>53</v>
+      </c>
       <c r="Q84" t="b">
         <v>0</v>
       </c>
@@ -5722,6 +6723,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>49</v>
+      </c>
       <c r="Q85" t="b">
         <v>0</v>
       </c>
@@ -5784,6 +6798,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>52</v>
+      </c>
       <c r="Q86" t="b">
         <v>0</v>
       </c>
@@ -5846,6 +6873,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>37</v>
+      </c>
       <c r="Q87" t="b">
         <v>0</v>
       </c>
@@ -5908,6 +6948,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>52</v>
+      </c>
       <c r="Q88" t="b">
         <v>0</v>
       </c>
@@ -5970,6 +7023,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>49</v>
+      </c>
       <c r="Q89" t="b">
         <v>0</v>
       </c>
@@ -6032,6 +7098,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>50</v>
+      </c>
       <c r="Q90" t="b">
         <v>0</v>
       </c>
@@ -6156,6 +7235,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>71</v>
+      </c>
       <c r="Q92" t="b">
         <v>0</v>
       </c>
@@ -6218,6 +7310,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>41</v>
+      </c>
       <c r="Q93" t="b">
         <v>0</v>
       </c>
@@ -6280,6 +7385,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>54</v>
+      </c>
       <c r="Q94" t="b">
         <v>0</v>
       </c>
@@ -6342,6 +7460,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>35</v>
+      </c>
       <c r="Q95" t="b">
         <v>0</v>
       </c>
@@ -6404,6 +7535,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>43</v>
+      </c>
       <c r="Q96" t="b">
         <v>0</v>
       </c>
@@ -6466,6 +7610,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>67</v>
+      </c>
       <c r="Q97" t="b">
         <v>1</v>
       </c>
@@ -6528,6 +7685,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>51</v>
+      </c>
       <c r="Q98" t="b">
         <v>0</v>
       </c>
@@ -6590,6 +7760,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>53</v>
+      </c>
       <c r="Q99" t="b">
         <v>0</v>
       </c>
@@ -6714,6 +7897,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>50</v>
+      </c>
       <c r="Q101" t="b">
         <v>0</v>
       </c>
@@ -6776,6 +7972,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>59</v>
+      </c>
       <c r="Q102" t="b">
         <v>0</v>
       </c>
@@ -6838,6 +8047,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>42</v>
+      </c>
       <c r="Q103" t="b">
         <v>0</v>
       </c>
@@ -6900,6 +8122,19 @@
           <t>RSP</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>63</v>
+      </c>
       <c r="Q104" t="b">
         <v>0</v>
       </c>
@@ -6962,6 +8197,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>34</v>
+      </c>
       <c r="Q105" t="b">
         <v>0</v>
       </c>
@@ -7024,6 +8272,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>53</v>
+      </c>
       <c r="Q106" t="b">
         <v>0</v>
       </c>
@@ -7086,6 +8347,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>40</v>
+      </c>
       <c r="Q107" t="b">
         <v>0</v>
       </c>
@@ -7148,6 +8422,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>42</v>
+      </c>
       <c r="Q108" t="b">
         <v>1</v>
       </c>
@@ -7210,6 +8497,19 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>45</v>
+      </c>
       <c r="Q109" t="b">
         <v>0</v>
       </c>
@@ -7272,6 +8572,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>62</v>
+      </c>
       <c r="Q110" t="b">
         <v>0</v>
       </c>
@@ -7334,6 +8647,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>64</v>
+      </c>
       <c r="Q111" t="b">
         <v>0</v>
       </c>
@@ -7458,8 +8784,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>39</v>
+      </c>
       <c r="Q113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
         <v>26</v>
@@ -7520,6 +8859,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>39</v>
+      </c>
       <c r="Q114" t="b">
         <v>0</v>
       </c>
@@ -7582,6 +8934,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>62</v>
+      </c>
       <c r="Q115" t="b">
         <v>0</v>
       </c>
@@ -7644,6 +9009,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>40</v>
+      </c>
       <c r="Q116" t="b">
         <v>0</v>
       </c>
@@ -7706,6 +9084,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>40</v>
+      </c>
       <c r="Q117" t="b">
         <v>0</v>
       </c>
@@ -7768,6 +9159,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>65</v>
+      </c>
       <c r="Q118" t="b">
         <v>0</v>
       </c>
@@ -7830,6 +9234,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>61</v>
+      </c>
       <c r="Q119" t="b">
         <v>0</v>
       </c>
@@ -7892,6 +9309,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>46</v>
+      </c>
       <c r="Q120" t="b">
         <v>0</v>
       </c>
@@ -7954,6 +9384,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>50</v>
+      </c>
       <c r="Q121" t="b">
         <v>0</v>
       </c>
@@ -8016,6 +9459,19 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>67</v>
+      </c>
       <c r="Q122" t="b">
         <v>0</v>
       </c>
@@ -8078,8 +9534,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>51</v>
+      </c>
       <c r="Q123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
         <v>26</v>
@@ -8202,6 +9671,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>35</v>
+      </c>
       <c r="Q125" t="b">
         <v>0</v>
       </c>
@@ -8264,6 +9746,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>51</v>
+      </c>
       <c r="Q126" t="b">
         <v>0</v>
       </c>
@@ -8326,6 +9821,19 @@
           <t>AgIMK</t>
         </is>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>37</v>
+      </c>
       <c r="Q127" t="b">
         <v>0</v>
       </c>
@@ -8388,6 +9896,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>30</v>
+      </c>
       <c r="Q128" t="b">
         <v>0</v>
       </c>
@@ -8450,6 +9971,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>54</v>
+      </c>
       <c r="Q129" t="b">
         <v>0</v>
       </c>
@@ -8512,6 +10046,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>54</v>
+      </c>
       <c r="Q130" t="b">
         <v>0</v>
       </c>
@@ -8574,6 +10121,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>65</v>
+      </c>
       <c r="Q131" t="b">
         <v>0</v>
       </c>
@@ -8636,6 +10196,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>42</v>
+      </c>
       <c r="Q132" t="b">
         <v>0</v>
       </c>
@@ -8698,6 +10271,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>46</v>
+      </c>
       <c r="Q133" t="b">
         <v>0</v>
       </c>
@@ -8760,6 +10346,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>48</v>
+      </c>
       <c r="Q134" t="b">
         <v>0</v>
       </c>
@@ -8822,6 +10421,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>54</v>
+      </c>
       <c r="Q135" t="b">
         <v>0</v>
       </c>
@@ -8884,6 +10496,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>26</v>
+      </c>
       <c r="Q136" t="b">
         <v>0</v>
       </c>
@@ -9008,6 +10633,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>26</v>
+      </c>
       <c r="Q138" t="b">
         <v>0</v>
       </c>
@@ -9070,6 +10708,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>53</v>
+      </c>
       <c r="Q139" t="b">
         <v>0</v>
       </c>
@@ -9132,6 +10783,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>31</v>
+      </c>
       <c r="Q140" t="b">
         <v>0</v>
       </c>
@@ -9194,6 +10858,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>40</v>
+      </c>
       <c r="Q141" t="b">
         <v>0</v>
       </c>
@@ -9256,6 +10933,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>50</v>
+      </c>
       <c r="Q142" t="b">
         <v>0</v>
       </c>
@@ -9318,6 +11008,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>45</v>
+      </c>
       <c r="Q143" t="b">
         <v>0</v>
       </c>
@@ -9380,6 +11083,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>49</v>
+      </c>
       <c r="Q144" t="b">
         <v>0</v>
       </c>
@@ -9442,6 +11158,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>52</v>
+      </c>
       <c r="Q145" t="b">
         <v>0</v>
       </c>
@@ -9504,6 +11233,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>38</v>
+      </c>
       <c r="Q146" t="b">
         <v>0</v>
       </c>
@@ -9566,6 +11308,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>54</v>
+      </c>
       <c r="Q147" t="b">
         <v>0</v>
       </c>
@@ -9628,6 +11383,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>58</v>
+      </c>
       <c r="Q148" t="b">
         <v>0</v>
       </c>
@@ -9752,6 +11520,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>50</v>
+      </c>
       <c r="Q150" t="b">
         <v>0</v>
       </c>
@@ -9814,6 +11595,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>45</v>
+      </c>
       <c r="Q151" t="b">
         <v>0</v>
       </c>
@@ -9876,6 +11670,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>29</v>
+      </c>
       <c r="Q152" t="b">
         <v>0</v>
       </c>
@@ -9938,6 +11745,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>45</v>
+      </c>
       <c r="Q153" t="b">
         <v>0</v>
       </c>
@@ -10000,6 +11820,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>45</v>
+      </c>
       <c r="Q154" t="b">
         <v>0</v>
       </c>
@@ -10062,6 +11895,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>39</v>
+      </c>
       <c r="Q155" t="b">
         <v>0</v>
       </c>
@@ -10124,6 +11970,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>64</v>
+      </c>
       <c r="Q156" t="b">
         <v>0</v>
       </c>
@@ -10186,6 +12045,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>67</v>
+      </c>
       <c r="Q157" t="b">
         <v>0</v>
       </c>
@@ -10248,6 +12120,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>44</v>
+      </c>
       <c r="Q158" t="b">
         <v>0</v>
       </c>
@@ -10310,6 +12195,19 @@
           <t>AgIMK</t>
         </is>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>39</v>
+      </c>
       <c r="Q159" t="b">
         <v>0</v>
       </c>
@@ -10372,6 +12270,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>35</v>
+      </c>
       <c r="Q160" t="b">
         <v>0</v>
       </c>
@@ -10434,6 +12345,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P161" t="n">
+        <v>34</v>
+      </c>
       <c r="Q161" t="b">
         <v>0</v>
       </c>
@@ -10496,6 +12420,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P162" t="n">
+        <v>56</v>
+      </c>
       <c r="Q162" t="b">
         <v>0</v>
       </c>
@@ -10620,6 +12557,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P164" t="n">
+        <v>49</v>
+      </c>
       <c r="Q164" t="b">
         <v>0</v>
       </c>
@@ -10682,6 +12632,19 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P165" t="n">
+        <v>49</v>
+      </c>
       <c r="Q165" t="b">
         <v>0</v>
       </c>
@@ -10744,6 +12707,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
+        <v>42</v>
+      </c>
       <c r="Q166" t="b">
         <v>0</v>
       </c>
@@ -10806,6 +12782,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P167" t="n">
+        <v>40</v>
+      </c>
       <c r="Q167" t="b">
         <v>0</v>
       </c>
@@ -10868,6 +12857,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P168" t="n">
+        <v>40</v>
+      </c>
       <c r="Q168" t="b">
         <v>0</v>
       </c>
@@ -10930,6 +12932,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P169" t="n">
+        <v>57</v>
+      </c>
       <c r="Q169" t="b">
         <v>0</v>
       </c>
@@ -10992,6 +13007,19 @@
           <t>AgIMK</t>
         </is>
       </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P170" t="n">
+        <v>38</v>
+      </c>
       <c r="Q170" t="b">
         <v>0</v>
       </c>
@@ -11054,6 +13082,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P171" t="n">
+        <v>43</v>
+      </c>
       <c r="Q171" t="b">
         <v>0</v>
       </c>
@@ -11116,6 +13157,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P172" t="n">
+        <v>43</v>
+      </c>
       <c r="Q172" t="b">
         <v>0</v>
       </c>
@@ -11178,6 +13232,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P173" t="n">
+        <v>56</v>
+      </c>
       <c r="Q173" t="b">
         <v>1</v>
       </c>
@@ -11240,6 +13307,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P174" t="n">
+        <v>67</v>
+      </c>
       <c r="Q174" t="b">
         <v>0</v>
       </c>
@@ -11302,6 +13382,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P175" t="n">
+        <v>50</v>
+      </c>
       <c r="Q175" t="b">
         <v>0</v>
       </c>
@@ -11364,6 +13457,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P176" t="n">
+        <v>44</v>
+      </c>
       <c r="Q176" t="b">
         <v>0</v>
       </c>
@@ -11488,6 +13594,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P178" t="n">
+        <v>26</v>
+      </c>
       <c r="Q178" t="b">
         <v>0</v>
       </c>
@@ -11550,6 +13669,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>53</v>
+      </c>
       <c r="Q179" t="b">
         <v>0</v>
       </c>
@@ -11612,6 +13744,19 @@
           <t>MDMK</t>
         </is>
       </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P180" t="n">
+        <v>47</v>
+      </c>
       <c r="Q180" t="b">
         <v>0</v>
       </c>
@@ -11674,6 +13819,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P181" t="n">
+        <v>38</v>
+      </c>
       <c r="Q181" t="b">
         <v>0</v>
       </c>
@@ -11736,6 +13894,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P182" t="n">
+        <v>38</v>
+      </c>
       <c r="Q182" t="b">
         <v>0</v>
       </c>
@@ -11798,6 +13969,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P183" t="n">
+        <v>42</v>
+      </c>
       <c r="Q183" t="b">
         <v>0</v>
       </c>
@@ -11860,6 +14044,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P184" t="n">
+        <v>76</v>
+      </c>
       <c r="Q184" t="b">
         <v>0</v>
       </c>
@@ -11922,6 +14119,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P185" t="n">
+        <v>58</v>
+      </c>
       <c r="Q185" t="b">
         <v>1</v>
       </c>
@@ -11984,8 +14194,21 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P186" t="n">
+        <v>51</v>
+      </c>
       <c r="Q186" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R186" t="n">
         <v>26</v>
@@ -12046,6 +14269,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P187" t="n">
+        <v>52</v>
+      </c>
       <c r="Q187" t="b">
         <v>0</v>
       </c>
@@ -12170,6 +14406,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P189" t="n">
+        <v>41</v>
+      </c>
       <c r="Q189" t="b">
         <v>0</v>
       </c>
@@ -12232,6 +14481,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P190" t="n">
+        <v>54</v>
+      </c>
       <c r="Q190" t="b">
         <v>0</v>
       </c>
@@ -12294,6 +14556,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P191" t="n">
+        <v>50</v>
+      </c>
       <c r="Q191" t="b">
         <v>0</v>
       </c>
@@ -12356,6 +14631,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P192" t="n">
+        <v>63</v>
+      </c>
       <c r="Q192" t="b">
         <v>0</v>
       </c>
@@ -12418,6 +14706,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P193" t="n">
+        <v>55</v>
+      </c>
       <c r="Q193" t="b">
         <v>0</v>
       </c>
@@ -12480,6 +14781,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P194" t="n">
+        <v>40</v>
+      </c>
       <c r="Q194" t="b">
         <v>0</v>
       </c>
@@ -12542,6 +14856,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P195" t="n">
+        <v>42</v>
+      </c>
       <c r="Q195" t="b">
         <v>0</v>
       </c>
@@ -12604,6 +14931,19 @@
           <t>AgIMK</t>
         </is>
       </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P196" t="n">
+        <v>43</v>
+      </c>
       <c r="Q196" t="b">
         <v>0</v>
       </c>
@@ -12666,6 +15006,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P197" t="n">
+        <v>29</v>
+      </c>
       <c r="Q197" t="b">
         <v>0</v>
       </c>
@@ -12728,6 +15081,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P198" t="n">
+        <v>57</v>
+      </c>
       <c r="Q198" t="b">
         <v>0</v>
       </c>
@@ -12790,6 +15156,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P199" t="n">
+        <v>46</v>
+      </c>
       <c r="Q199" t="b">
         <v>0</v>
       </c>
@@ -12852,8 +15231,21 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P200" t="n">
+        <v>49</v>
+      </c>
       <c r="Q200" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R200" t="n">
         <v>26</v>
@@ -12914,6 +15306,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P201" t="n">
+        <v>51</v>
+      </c>
       <c r="Q201" t="b">
         <v>1</v>
       </c>
@@ -12976,6 +15381,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P202" t="n">
+        <v>63</v>
+      </c>
       <c r="Q202" t="b">
         <v>0</v>
       </c>
@@ -13100,6 +15518,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P204" t="n">
+        <v>61</v>
+      </c>
       <c r="Q204" t="b">
         <v>0</v>
       </c>
@@ -13162,6 +15593,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P205" t="n">
+        <v>37</v>
+      </c>
       <c r="Q205" t="b">
         <v>0</v>
       </c>
@@ -13224,6 +15668,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P206" t="n">
+        <v>42</v>
+      </c>
       <c r="Q206" t="b">
         <v>0</v>
       </c>
@@ -13286,6 +15743,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P207" t="n">
+        <v>38</v>
+      </c>
       <c r="Q207" t="b">
         <v>0</v>
       </c>
@@ -13348,6 +15818,19 @@
           <t>MDMK</t>
         </is>
       </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P208" t="n">
+        <v>44</v>
+      </c>
       <c r="Q208" t="b">
         <v>0</v>
       </c>
@@ -13410,8 +15893,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P209" t="n">
+        <v>35</v>
+      </c>
       <c r="Q209" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R209" t="n">
         <v>26</v>
@@ -13472,8 +15968,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P210" t="n">
+        <v>59</v>
+      </c>
       <c r="Q210" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R210" t="n">
         <v>26</v>
@@ -13534,6 +16043,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P211" t="n">
+        <v>40</v>
+      </c>
       <c r="Q211" t="b">
         <v>0</v>
       </c>
@@ -13596,6 +16118,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P212" t="n">
+        <v>55</v>
+      </c>
       <c r="Q212" t="b">
         <v>0</v>
       </c>
@@ -13658,8 +16193,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P213" t="n">
+        <v>56</v>
+      </c>
       <c r="Q213" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R213" t="n">
         <v>26</v>
@@ -13720,6 +16268,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P214" t="n">
+        <v>51</v>
+      </c>
       <c r="Q214" t="b">
         <v>0</v>
       </c>
@@ -13782,6 +16343,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P215" t="n">
+        <v>56</v>
+      </c>
       <c r="Q215" t="b">
         <v>1</v>
       </c>
@@ -13844,6 +16418,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P216" t="n">
+        <v>35</v>
+      </c>
       <c r="Q216" t="b">
         <v>0</v>
       </c>
@@ -13968,6 +16555,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P218" t="n">
+        <v>64</v>
+      </c>
       <c r="Q218" t="b">
         <v>0</v>
       </c>
@@ -14030,6 +16630,19 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P219" t="n">
+        <v>56</v>
+      </c>
       <c r="Q219" t="b">
         <v>0</v>
       </c>
@@ -14092,6 +16705,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P220" t="n">
+        <v>28</v>
+      </c>
       <c r="Q220" t="b">
         <v>0</v>
       </c>
@@ -14154,6 +16780,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P221" t="n">
+        <v>45</v>
+      </c>
       <c r="Q221" t="b">
         <v>0</v>
       </c>
@@ -14216,6 +16855,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P222" t="n">
+        <v>34</v>
+      </c>
       <c r="Q222" t="b">
         <v>0</v>
       </c>
@@ -14278,6 +16930,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P223" t="n">
+        <v>37</v>
+      </c>
       <c r="Q223" t="b">
         <v>0</v>
       </c>
@@ -14340,6 +17005,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P224" t="n">
+        <v>28</v>
+      </c>
       <c r="Q224" t="b">
         <v>0</v>
       </c>
@@ -14402,6 +17080,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P225" t="n">
+        <v>40</v>
+      </c>
       <c r="Q225" t="b">
         <v>0</v>
       </c>
@@ -14464,6 +17155,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P226" t="n">
+        <v>36</v>
+      </c>
       <c r="Q226" t="b">
         <v>0</v>
       </c>
@@ -14526,6 +17230,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P227" t="n">
+        <v>44</v>
+      </c>
       <c r="Q227" t="b">
         <v>1</v>
       </c>
@@ -14588,6 +17305,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P228" t="n">
+        <v>64</v>
+      </c>
       <c r="Q228" t="b">
         <v>0</v>
       </c>
@@ -14650,6 +17380,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P229" t="n">
+        <v>40</v>
+      </c>
       <c r="Q229" t="b">
         <v>0</v>
       </c>
@@ -14774,6 +17517,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P231" t="n">
+        <v>60</v>
+      </c>
       <c r="Q231" t="b">
         <v>0</v>
       </c>
@@ -14836,6 +17592,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P232" t="n">
+        <v>61</v>
+      </c>
       <c r="Q232" t="b">
         <v>0</v>
       </c>
@@ -14898,6 +17667,19 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P233" t="n">
+        <v>63</v>
+      </c>
       <c r="Q233" t="b">
         <v>0</v>
       </c>
@@ -14960,6 +17742,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P234" t="n">
+        <v>45</v>
+      </c>
       <c r="Q234" t="b">
         <v>0</v>
       </c>
@@ -15022,6 +17817,19 @@
           <t>TAVK</t>
         </is>
       </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P235" t="n">
+        <v>33</v>
+      </c>
       <c r="Q235" t="b">
         <v>0</v>
       </c>
@@ -15084,6 +17892,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P236" t="n">
+        <v>26</v>
+      </c>
       <c r="Q236" t="b">
         <v>0</v>
       </c>
@@ -15146,6 +17967,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P237" t="n">
+        <v>26</v>
+      </c>
       <c r="Q237" t="b">
         <v>0</v>
       </c>
@@ -15208,6 +18042,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P238" t="n">
+        <v>38</v>
+      </c>
       <c r="Q238" t="b">
         <v>0</v>
       </c>
@@ -15270,6 +18117,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P239" t="n">
+        <v>57</v>
+      </c>
       <c r="Q239" t="b">
         <v>0</v>
       </c>
@@ -15332,6 +18192,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P240" t="n">
+        <v>69</v>
+      </c>
       <c r="Q240" t="b">
         <v>0</v>
       </c>
@@ -15394,8 +18267,21 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P241" t="n">
+        <v>72</v>
+      </c>
       <c r="Q241" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R241" t="n">
         <v>26</v>
@@ -15456,8 +18342,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P242" t="n">
+        <v>46</v>
+      </c>
       <c r="Q242" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R242" t="n">
         <v>26</v>
@@ -15580,6 +18479,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P244" t="n">
+        <v>63</v>
+      </c>
       <c r="Q244" t="b">
         <v>0</v>
       </c>
@@ -15642,6 +18554,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P245" t="n">
+        <v>47</v>
+      </c>
       <c r="Q245" t="b">
         <v>0</v>
       </c>
@@ -15704,6 +18629,19 @@
           <t>MDMK</t>
         </is>
       </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P246" t="n">
+        <v>51</v>
+      </c>
       <c r="Q246" t="b">
         <v>0</v>
       </c>
@@ -15766,6 +18704,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P247" t="n">
+        <v>39</v>
+      </c>
       <c r="Q247" t="b">
         <v>0</v>
       </c>
@@ -15828,6 +18779,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P248" t="n">
+        <v>26</v>
+      </c>
       <c r="Q248" t="b">
         <v>0</v>
       </c>
@@ -15890,6 +18854,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P249" t="n">
+        <v>39</v>
+      </c>
       <c r="Q249" t="b">
         <v>0</v>
       </c>
@@ -15952,6 +18929,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P250" t="n">
+        <v>61</v>
+      </c>
       <c r="Q250" t="b">
         <v>0</v>
       </c>
@@ -16014,6 +19004,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P251" t="n">
+        <v>53</v>
+      </c>
       <c r="Q251" t="b">
         <v>0</v>
       </c>
@@ -16076,6 +19079,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P252" t="n">
+        <v>44</v>
+      </c>
       <c r="Q252" t="b">
         <v>0</v>
       </c>
@@ -16138,6 +19154,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P253" t="n">
+        <v>43</v>
+      </c>
       <c r="Q253" t="b">
         <v>0</v>
       </c>
@@ -16200,6 +19229,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P254" t="n">
+        <v>44</v>
+      </c>
       <c r="Q254" t="b">
         <v>0</v>
       </c>
@@ -16262,6 +19304,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P255" t="n">
+        <v>52</v>
+      </c>
       <c r="Q255" t="b">
         <v>0</v>
       </c>
@@ -16324,8 +19379,21 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P256" t="n">
+        <v>67</v>
+      </c>
       <c r="Q256" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R256" t="n">
         <v>26</v>
@@ -16386,6 +19454,19 @@
           <t>VCK</t>
         </is>
       </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P257" t="n">
+        <v>40</v>
+      </c>
       <c r="Q257" t="b">
         <v>0</v>
       </c>
@@ -16510,6 +19591,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P259" t="n">
+        <v>28</v>
+      </c>
       <c r="Q259" t="b">
         <v>0</v>
       </c>
@@ -16572,6 +19666,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P260" t="n">
+        <v>47</v>
+      </c>
       <c r="Q260" t="b">
         <v>0</v>
       </c>
@@ -16634,6 +19741,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P261" t="n">
+        <v>55</v>
+      </c>
       <c r="Q261" t="b">
         <v>0</v>
       </c>
@@ -16696,6 +19816,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P262" t="n">
+        <v>45</v>
+      </c>
       <c r="Q262" t="b">
         <v>0</v>
       </c>
@@ -16758,6 +19891,19 @@
           <t>TAVK</t>
         </is>
       </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P263" t="n">
+        <v>34</v>
+      </c>
       <c r="Q263" t="b">
         <v>0</v>
       </c>
@@ -16820,6 +19966,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P264" t="n">
+        <v>44</v>
+      </c>
       <c r="Q264" t="b">
         <v>0</v>
       </c>
@@ -16882,6 +20041,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P265" t="n">
+        <v>50</v>
+      </c>
       <c r="Q265" t="b">
         <v>0</v>
       </c>
@@ -16944,6 +20116,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P266" t="n">
+        <v>46</v>
+      </c>
       <c r="Q266" t="b">
         <v>0</v>
       </c>
@@ -17006,6 +20191,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P267" t="n">
+        <v>48</v>
+      </c>
       <c r="Q267" t="b">
         <v>0</v>
       </c>
@@ -17130,6 +20328,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P269" t="n">
+        <v>35</v>
+      </c>
       <c r="Q269" t="b">
         <v>0</v>
       </c>
@@ -17192,6 +20403,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P270" t="n">
+        <v>60</v>
+      </c>
       <c r="Q270" t="b">
         <v>0</v>
       </c>
@@ -17254,6 +20478,19 @@
           <t>CPI(ML)(L)</t>
         </is>
       </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P271" t="n">
+        <v>50</v>
+      </c>
       <c r="Q271" t="b">
         <v>0</v>
       </c>
@@ -17316,6 +20553,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P272" t="n">
+        <v>31</v>
+      </c>
       <c r="Q272" t="b">
         <v>0</v>
       </c>
@@ -17378,6 +20628,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P273" t="n">
+        <v>51</v>
+      </c>
       <c r="Q273" t="b">
         <v>0</v>
       </c>
@@ -17440,6 +20703,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P274" t="n">
+        <v>29</v>
+      </c>
       <c r="Q274" t="b">
         <v>0</v>
       </c>
@@ -17502,6 +20778,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P275" t="n">
+        <v>45</v>
+      </c>
       <c r="Q275" t="b">
         <v>0</v>
       </c>
@@ -17564,6 +20853,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P276" t="n">
+        <v>54</v>
+      </c>
       <c r="Q276" t="b">
         <v>0</v>
       </c>
@@ -17626,6 +20928,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P277" t="n">
+        <v>61</v>
+      </c>
       <c r="Q277" t="b">
         <v>0</v>
       </c>
@@ -17688,6 +21003,19 @@
           <t>VCK</t>
         </is>
       </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P278" t="n">
+        <v>60</v>
+      </c>
       <c r="Q278" t="b">
         <v>0</v>
       </c>
@@ -17750,6 +21078,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P279" t="n">
+        <v>39</v>
+      </c>
       <c r="Q279" t="b">
         <v>0</v>
       </c>
@@ -17812,6 +21153,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P280" t="n">
+        <v>40</v>
+      </c>
       <c r="Q280" t="b">
         <v>0</v>
       </c>
@@ -17936,6 +21290,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P282" t="n">
+        <v>31</v>
+      </c>
       <c r="Q282" t="b">
         <v>0</v>
       </c>
@@ -17998,6 +21365,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P283" t="n">
+        <v>27</v>
+      </c>
       <c r="Q283" t="b">
         <v>0</v>
       </c>
@@ -18060,6 +21440,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P284" t="n">
+        <v>43</v>
+      </c>
       <c r="Q284" t="b">
         <v>0</v>
       </c>
@@ -18122,6 +21515,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P285" t="n">
+        <v>31</v>
+      </c>
       <c r="Q285" t="b">
         <v>0</v>
       </c>
@@ -18184,6 +21590,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P286" t="n">
+        <v>40</v>
+      </c>
       <c r="Q286" t="b">
         <v>0</v>
       </c>
@@ -18246,6 +21665,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P287" t="n">
+        <v>50</v>
+      </c>
       <c r="Q287" t="b">
         <v>0</v>
       </c>
@@ -18308,6 +21740,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P288" t="n">
+        <v>64</v>
+      </c>
       <c r="Q288" t="b">
         <v>0</v>
       </c>
@@ -18370,6 +21815,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P289" t="n">
+        <v>45</v>
+      </c>
       <c r="Q289" t="b">
         <v>0</v>
       </c>
@@ -18432,6 +21890,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P290" t="n">
+        <v>53</v>
+      </c>
       <c r="Q290" t="b">
         <v>0</v>
       </c>
@@ -18494,6 +21965,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P291" t="n">
+        <v>67</v>
+      </c>
       <c r="Q291" t="b">
         <v>0</v>
       </c>
@@ -18618,6 +22102,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P293" t="n">
+        <v>35</v>
+      </c>
       <c r="Q293" t="b">
         <v>0</v>
       </c>
@@ -18680,6 +22177,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P294" t="n">
+        <v>59</v>
+      </c>
       <c r="Q294" t="b">
         <v>0</v>
       </c>
@@ -18742,6 +22252,19 @@
           <t>IJK</t>
         </is>
       </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P295" t="n">
+        <v>49</v>
+      </c>
       <c r="Q295" t="b">
         <v>0</v>
       </c>
@@ -18804,6 +22327,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P296" t="n">
+        <v>25</v>
+      </c>
       <c r="Q296" t="b">
         <v>0</v>
       </c>
@@ -18866,6 +22402,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P297" t="n">
+        <v>26</v>
+      </c>
       <c r="Q297" t="b">
         <v>0</v>
       </c>
@@ -18928,6 +22477,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P298" t="n">
+        <v>74</v>
+      </c>
       <c r="Q298" t="b">
         <v>0</v>
       </c>
@@ -18990,6 +22552,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P299" t="n">
+        <v>63</v>
+      </c>
       <c r="Q299" t="b">
         <v>0</v>
       </c>
@@ -19052,6 +22627,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P300" t="n">
+        <v>34</v>
+      </c>
       <c r="Q300" t="b">
         <v>0</v>
       </c>
@@ -19114,6 +22702,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P301" t="n">
+        <v>53</v>
+      </c>
       <c r="Q301" t="b">
         <v>0</v>
       </c>
@@ -19176,6 +22777,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P302" t="n">
+        <v>42</v>
+      </c>
       <c r="Q302" t="b">
         <v>0</v>
       </c>
@@ -19238,6 +22852,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P303" t="n">
+        <v>30</v>
+      </c>
       <c r="Q303" t="b">
         <v>0</v>
       </c>
@@ -19362,6 +22989,19 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P305" t="n">
+        <v>48</v>
+      </c>
       <c r="Q305" t="b">
         <v>0</v>
       </c>
@@ -19424,6 +23064,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P306" t="n">
+        <v>65</v>
+      </c>
       <c r="Q306" t="b">
         <v>0</v>
       </c>
@@ -19486,6 +23139,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P307" t="n">
+        <v>43</v>
+      </c>
       <c r="Q307" t="b">
         <v>0</v>
       </c>
@@ -19548,6 +23214,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P308" t="n">
+        <v>58</v>
+      </c>
       <c r="Q308" t="b">
         <v>0</v>
       </c>
@@ -19610,6 +23289,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P309" t="n">
+        <v>41</v>
+      </c>
       <c r="Q309" t="b">
         <v>0</v>
       </c>
@@ -19672,6 +23364,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P310" t="n">
+        <v>46</v>
+      </c>
       <c r="Q310" t="b">
         <v>0</v>
       </c>
@@ -19796,6 +23501,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P312" t="n">
+        <v>47</v>
+      </c>
       <c r="Q312" t="b">
         <v>0</v>
       </c>
@@ -19858,6 +23576,19 @@
           <t>MDMK</t>
         </is>
       </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P313" t="n">
+        <v>64</v>
+      </c>
       <c r="Q313" t="b">
         <v>0</v>
       </c>
@@ -19920,6 +23651,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P314" t="n">
+        <v>53</v>
+      </c>
       <c r="Q314" t="b">
         <v>0</v>
       </c>
@@ -19982,6 +23726,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P315" t="n">
+        <v>35</v>
+      </c>
       <c r="Q315" t="b">
         <v>0</v>
       </c>
@@ -20044,6 +23801,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P316" t="n">
+        <v>43</v>
+      </c>
       <c r="Q316" t="b">
         <v>0</v>
       </c>
@@ -20106,6 +23876,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P317" t="n">
+        <v>38</v>
+      </c>
       <c r="Q317" t="b">
         <v>0</v>
       </c>
@@ -20168,6 +23951,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P318" t="n">
+        <v>61</v>
+      </c>
       <c r="Q318" t="b">
         <v>0</v>
       </c>
@@ -20230,6 +24026,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P319" t="n">
+        <v>31</v>
+      </c>
       <c r="Q319" t="b">
         <v>0</v>
       </c>
@@ -20292,6 +24101,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P320" t="n">
+        <v>44</v>
+      </c>
       <c r="Q320" t="b">
         <v>0</v>
       </c>
@@ -20354,6 +24176,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P321" t="n">
+        <v>44</v>
+      </c>
       <c r="Q321" t="b">
         <v>0</v>
       </c>
@@ -20416,6 +24251,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P322" t="n">
+        <v>46</v>
+      </c>
       <c r="Q322" t="b">
         <v>0</v>
       </c>
@@ -20540,6 +24388,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P324" t="n">
+        <v>50</v>
+      </c>
       <c r="Q324" t="b">
         <v>0</v>
       </c>
@@ -20602,6 +24463,19 @@
           <t>VCK</t>
         </is>
       </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P325" t="n">
+        <v>46</v>
+      </c>
       <c r="Q325" t="b">
         <v>0</v>
       </c>
@@ -20664,6 +24538,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P326" t="n">
+        <v>39</v>
+      </c>
       <c r="Q326" t="b">
         <v>0</v>
       </c>
@@ -20726,6 +24613,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P327" t="n">
+        <v>32</v>
+      </c>
       <c r="Q327" t="b">
         <v>0</v>
       </c>
@@ -20788,6 +24688,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P328" t="n">
+        <v>60</v>
+      </c>
       <c r="Q328" t="b">
         <v>0</v>
       </c>
@@ -20850,6 +24763,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P329" t="n">
+        <v>61</v>
+      </c>
       <c r="Q329" t="b">
         <v>0</v>
       </c>
@@ -20912,6 +24838,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P330" t="n">
+        <v>54</v>
+      </c>
       <c r="Q330" t="b">
         <v>1</v>
       </c>
@@ -20974,6 +24913,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P331" t="n">
+        <v>37</v>
+      </c>
       <c r="Q331" t="b">
         <v>0</v>
       </c>
@@ -21098,6 +25050,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P333" t="n">
+        <v>38</v>
+      </c>
       <c r="Q333" t="b">
         <v>0</v>
       </c>
@@ -21160,6 +25125,19 @@
           <t>SDPI</t>
         </is>
       </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P334" t="n">
+        <v>32</v>
+      </c>
       <c r="Q334" t="b">
         <v>0</v>
       </c>
@@ -21222,6 +25200,19 @@
           <t>DMDK</t>
         </is>
       </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P335" t="n">
+        <v>31</v>
+      </c>
       <c r="Q335" t="b">
         <v>0</v>
       </c>
@@ -21284,6 +25275,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P336" t="n">
+        <v>36</v>
+      </c>
       <c r="Q336" t="b">
         <v>0</v>
       </c>
@@ -21346,6 +25350,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P337" t="n">
+        <v>28</v>
+      </c>
       <c r="Q337" t="b">
         <v>0</v>
       </c>
@@ -21408,6 +25425,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P338" t="n">
+        <v>57</v>
+      </c>
       <c r="Q338" t="b">
         <v>0</v>
       </c>
@@ -21470,6 +25500,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P339" t="n">
+        <v>30</v>
+      </c>
       <c r="Q339" t="b">
         <v>0</v>
       </c>
@@ -21532,6 +25575,19 @@
           <t>DMK</t>
         </is>
       </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P340" t="n">
+        <v>43</v>
+      </c>
       <c r="Q340" t="b">
         <v>0</v>
       </c>
@@ -21594,6 +25650,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P341" t="n">
+        <v>66</v>
+      </c>
       <c r="Q341" t="b">
         <v>0</v>
       </c>
@@ -21656,6 +25725,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P342" t="n">
+        <v>53</v>
+      </c>
       <c r="Q342" t="b">
         <v>0</v>
       </c>
@@ -21718,6 +25800,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P343" t="n">
+        <v>39</v>
+      </c>
       <c r="Q343" t="b">
         <v>0</v>
       </c>
@@ -21780,6 +25875,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P344" t="n">
+        <v>37</v>
+      </c>
       <c r="Q344" t="b">
         <v>0</v>
       </c>
@@ -21904,6 +26012,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P346" t="n">
+        <v>39</v>
+      </c>
       <c r="Q346" t="b">
         <v>0</v>
       </c>
@@ -21966,6 +26087,19 @@
           <t>SDPI</t>
         </is>
       </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P347" t="n">
+        <v>39</v>
+      </c>
       <c r="Q347" t="b">
         <v>0</v>
       </c>
@@ -22028,6 +26162,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P348" t="n">
+        <v>43</v>
+      </c>
       <c r="Q348" t="b">
         <v>0</v>
       </c>
@@ -22090,6 +26237,19 @@
           <t>NTK</t>
         </is>
       </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P349" t="n">
+        <v>29</v>
+      </c>
       <c r="Q349" t="b">
         <v>0</v>
       </c>
@@ -22152,6 +26312,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P350" t="n">
+        <v>44</v>
+      </c>
       <c r="Q350" t="b">
         <v>0</v>
       </c>
@@ -22214,6 +26387,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P351" t="n">
+        <v>32</v>
+      </c>
       <c r="Q351" t="b">
         <v>0</v>
       </c>
@@ -22276,6 +26462,19 @@
           <t>CPI(ML)(L)</t>
         </is>
       </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P352" t="n">
+        <v>54</v>
+      </c>
       <c r="Q352" t="b">
         <v>0</v>
       </c>
@@ -22338,6 +26537,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P353" t="n">
+        <v>69</v>
+      </c>
       <c r="Q353" t="b">
         <v>0</v>
       </c>
@@ -22400,8 +26612,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P354" t="n">
+        <v>62</v>
+      </c>
       <c r="Q354" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R354" t="n">
         <v>26</v>
@@ -22462,6 +26687,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P355" t="n">
+        <v>53</v>
+      </c>
       <c r="Q355" t="b">
         <v>0</v>
       </c>
@@ -22524,6 +26762,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P356" t="n">
+        <v>58</v>
+      </c>
       <c r="Q356" t="b">
         <v>0</v>
       </c>
@@ -22586,6 +26837,19 @@
           <t>SDPI</t>
         </is>
       </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P357" t="n">
+        <v>67</v>
+      </c>
       <c r="Q357" t="b">
         <v>0</v>
       </c>
@@ -22648,6 +26912,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P358" t="n">
+        <v>41</v>
+      </c>
       <c r="Q358" t="b">
         <v>0</v>
       </c>
@@ -22772,6 +27049,19 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P360" t="n">
+        <v>60</v>
+      </c>
       <c r="Q360" t="b">
         <v>0</v>
       </c>
@@ -22834,6 +27124,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P361" t="n">
+        <v>66</v>
+      </c>
       <c r="Q361" t="b">
         <v>0</v>
       </c>
@@ -22896,6 +27199,19 @@
           <t>PMK</t>
         </is>
       </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P362" t="n">
+        <v>40</v>
+      </c>
       <c r="Q362" t="b">
         <v>0</v>
       </c>
@@ -22958,6 +27274,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P363" t="n">
+        <v>73</v>
+      </c>
       <c r="Q363" t="b">
         <v>0</v>
       </c>
@@ -23020,6 +27349,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P364" t="n">
+        <v>51</v>
+      </c>
       <c r="Q364" t="b">
         <v>1</v>
       </c>
@@ -23082,6 +27424,19 @@
           <t>AINRC</t>
         </is>
       </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P365" t="n">
+        <v>59</v>
+      </c>
       <c r="Q365" t="b">
         <v>0</v>
       </c>
@@ -23144,8 +27499,21 @@
           <t>AIADMK</t>
         </is>
       </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P366" t="n">
+        <v>50</v>
+      </c>
       <c r="Q366" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R366" t="n">
         <v>26</v>
@@ -23206,6 +27574,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P367" t="n">
+        <v>34</v>
+      </c>
       <c r="Q367" t="b">
         <v>0</v>
       </c>
@@ -23268,6 +27649,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P368" t="n">
+        <v>63</v>
+      </c>
       <c r="Q368" t="b">
         <v>0</v>
       </c>
@@ -23392,6 +27786,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P370" t="n">
+        <v>30</v>
+      </c>
       <c r="Q370" t="b">
         <v>0</v>
       </c>
@@ -23454,6 +27861,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P371" t="n">
+        <v>61</v>
+      </c>
       <c r="Q371" t="b">
         <v>0</v>
       </c>
@@ -23516,6 +27936,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P372" t="n">
+        <v>48</v>
+      </c>
       <c r="Q372" t="b">
         <v>0</v>
       </c>
@@ -23578,6 +28011,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P373" t="n">
+        <v>58</v>
+      </c>
       <c r="Q373" t="b">
         <v>0</v>
       </c>
@@ -23640,6 +28086,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P374" t="n">
+        <v>31</v>
+      </c>
       <c r="Q374" t="b">
         <v>0</v>
       </c>
@@ -23702,8 +28161,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P375" t="n">
+        <v>38</v>
+      </c>
       <c r="Q375" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R375" t="n">
         <v>26</v>

--- a/static/data/exports/Retro_PY_AE_2016.xlsx
+++ b/static/data/exports/Retro_PY_AE_2016.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -658,7 +658,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -808,7 +808,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -883,7 +883,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -1727,11 +1727,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>22291</v>
+        <v>22297</v>
       </c>
       <c r="E18" t="n">
         <v>1484</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P61" t="n">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P75" t="n">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P82" t="n">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P83" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P85" t="n">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P86" t="n">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P87" t="n">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P89" t="n">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P90" t="n">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P94" t="n">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P95" t="n">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P96" t="n">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P97" t="n">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P99" t="n">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P103" t="n">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P116" t="n">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P117" t="n">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P118" t="n">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P119" t="n">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P121" t="n">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P123" t="n">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P125" t="n">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P126" t="n">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P131" t="n">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P133" t="n">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P134" t="n">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P135" t="n">
@@ -10460,11 +10460,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>22291</v>
+        <v>22297</v>
       </c>
       <c r="E136" t="n">
         <v>739</v>
@@ -10503,7 +10503,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -10715,7 +10715,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -10790,7 +10790,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -11165,7 +11165,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P145" t="n">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P146" t="n">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P147" t="n">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P148" t="n">
@@ -11527,7 +11527,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -11602,7 +11602,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P151" t="n">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P152" t="n">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P154" t="n">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P155" t="n">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P156" t="n">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P157" t="n">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P158" t="n">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P159" t="n">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P160" t="n">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P161" t="n">
@@ -12427,7 +12427,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P162" t="n">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P164" t="n">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P165" t="n">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P166" t="n">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P167" t="n">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P168" t="n">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P169" t="n">
@@ -13014,7 +13014,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P170" t="n">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P171" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P172" t="n">
@@ -13239,7 +13239,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P173" t="n">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P174" t="n">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P175" t="n">
@@ -13464,7 +13464,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P176" t="n">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P178" t="n">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P179" t="n">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P180" t="n">
@@ -13826,7 +13826,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P181" t="n">
@@ -13901,7 +13901,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P182" t="n">
@@ -13976,7 +13976,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P183" t="n">
@@ -14051,7 +14051,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P184" t="n">
@@ -14126,7 +14126,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P185" t="n">
@@ -14201,7 +14201,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P186" t="n">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P187" t="n">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P189" t="n">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P190" t="n">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P191" t="n">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P192" t="n">
@@ -14713,7 +14713,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P193" t="n">
@@ -14788,7 +14788,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P194" t="n">
@@ -14863,7 +14863,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P195" t="n">
@@ -14938,7 +14938,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P196" t="n">
@@ -15013,7 +15013,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P197" t="n">
@@ -15088,7 +15088,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P198" t="n">
@@ -15163,7 +15163,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P199" t="n">
@@ -15238,7 +15238,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P200" t="n">
@@ -15313,7 +15313,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P201" t="n">
@@ -15388,7 +15388,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P202" t="n">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P204" t="n">
@@ -15675,7 +15675,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P206" t="n">
@@ -15750,7 +15750,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P207" t="n">
@@ -15825,7 +15825,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P208" t="n">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P209" t="n">
@@ -15975,7 +15975,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P210" t="n">
@@ -16050,7 +16050,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P211" t="n">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P212" t="n">
@@ -16200,7 +16200,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P213" t="n">
@@ -16275,7 +16275,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P214" t="n">
@@ -16350,7 +16350,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P215" t="n">
@@ -16425,7 +16425,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P216" t="n">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P218" t="n">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P219" t="n">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P220" t="n">
@@ -16787,7 +16787,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P221" t="n">
@@ -16862,7 +16862,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P222" t="n">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P223" t="n">
@@ -17012,7 +17012,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P224" t="n">
@@ -17087,7 +17087,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P225" t="n">
@@ -17162,7 +17162,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P226" t="n">
@@ -17237,7 +17237,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P227" t="n">
@@ -17312,7 +17312,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P228" t="n">
@@ -17387,7 +17387,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P229" t="n">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P231" t="n">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P232" t="n">
@@ -17674,7 +17674,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P233" t="n">
@@ -17749,7 +17749,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P234" t="n">
@@ -17824,7 +17824,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P235" t="n">
@@ -17899,7 +17899,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P236" t="n">
@@ -17974,7 +17974,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P237" t="n">
@@ -18049,7 +18049,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P238" t="n">
@@ -18124,7 +18124,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P239" t="n">
@@ -18199,7 +18199,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P240" t="n">
@@ -18274,7 +18274,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P241" t="n">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P242" t="n">
@@ -18486,7 +18486,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P244" t="n">
@@ -18561,7 +18561,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P245" t="n">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P246" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P247" t="n">
@@ -18786,7 +18786,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P248" t="n">
@@ -18861,7 +18861,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P249" t="n">
@@ -18936,7 +18936,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P250" t="n">
@@ -19011,7 +19011,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P251" t="n">
@@ -19086,7 +19086,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P252" t="n">
@@ -19161,7 +19161,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P253" t="n">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P254" t="n">
@@ -19311,7 +19311,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P255" t="n">
@@ -19386,7 +19386,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P256" t="n">
@@ -19461,7 +19461,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P257" t="n">
@@ -19598,7 +19598,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P259" t="n">
@@ -19673,7 +19673,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P260" t="n">
@@ -19748,7 +19748,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P261" t="n">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P262" t="n">
@@ -19898,7 +19898,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P263" t="n">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P264" t="n">
@@ -20048,7 +20048,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P265" t="n">
@@ -20123,7 +20123,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P266" t="n">
@@ -20198,7 +20198,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P267" t="n">
@@ -20335,7 +20335,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P269" t="n">
@@ -20410,7 +20410,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P270" t="n">
@@ -20485,7 +20485,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P271" t="n">
@@ -20560,7 +20560,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P272" t="n">
@@ -20635,7 +20635,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P273" t="n">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P274" t="n">
@@ -20785,7 +20785,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P275" t="n">
@@ -20860,7 +20860,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P276" t="n">
@@ -20935,7 +20935,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P277" t="n">
@@ -21010,7 +21010,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P278" t="n">
@@ -21085,7 +21085,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P279" t="n">
@@ -21160,7 +21160,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P280" t="n">
@@ -21297,7 +21297,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P282" t="n">
@@ -21372,7 +21372,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P283" t="n">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P284" t="n">
@@ -21522,7 +21522,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P285" t="n">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P286" t="n">
@@ -21672,7 +21672,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P287" t="n">
@@ -21747,7 +21747,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P288" t="n">
@@ -21822,7 +21822,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P289" t="n">
@@ -21854,11 +21854,11 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>22291</v>
+        <v>22297</v>
       </c>
       <c r="E290" t="n">
         <v>457</v>
@@ -21897,7 +21897,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P290" t="n">
@@ -21972,7 +21972,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P291" t="n">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P293" t="n">
@@ -22184,7 +22184,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P294" t="n">
@@ -22259,7 +22259,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P295" t="n">
@@ -22334,7 +22334,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P296" t="n">
@@ -22409,7 +22409,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P297" t="n">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P298" t="n">
@@ -22559,7 +22559,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P299" t="n">
@@ -22634,7 +22634,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P300" t="n">
@@ -22709,7 +22709,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P301" t="n">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P302" t="n">
@@ -22859,7 +22859,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P303" t="n">
@@ -22996,7 +22996,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P305" t="n">
@@ -23071,7 +23071,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P306" t="n">
@@ -23146,7 +23146,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P307" t="n">
@@ -23221,7 +23221,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P308" t="n">
@@ -23296,7 +23296,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P309" t="n">
@@ -23371,7 +23371,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P310" t="n">
@@ -23508,7 +23508,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P312" t="n">
@@ -23583,7 +23583,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P313" t="n">
@@ -23658,7 +23658,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P314" t="n">
@@ -23733,7 +23733,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P315" t="n">
@@ -23808,7 +23808,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P316" t="n">
@@ -23883,7 +23883,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -23958,7 +23958,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P318" t="n">
@@ -24033,7 +24033,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P319" t="n">
@@ -24108,7 +24108,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P320" t="n">
@@ -24183,7 +24183,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P321" t="n">
@@ -24258,7 +24258,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P322" t="n">
@@ -24395,7 +24395,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P324" t="n">
@@ -24470,7 +24470,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P325" t="n">
@@ -24545,7 +24545,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P326" t="n">
@@ -24620,7 +24620,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P327" t="n">
@@ -24695,7 +24695,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P328" t="n">
@@ -24770,7 +24770,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P329" t="n">
@@ -24845,7 +24845,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P330" t="n">
@@ -24920,7 +24920,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P331" t="n">
@@ -25057,7 +25057,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P333" t="n">
@@ -25132,7 +25132,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P334" t="n">
@@ -25207,7 +25207,7 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P335" t="n">
@@ -25282,7 +25282,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P336" t="n">
@@ -25357,7 +25357,7 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P337" t="n">
@@ -25432,7 +25432,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P338" t="n">
@@ -25507,7 +25507,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P339" t="n">
@@ -25582,7 +25582,7 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P340" t="n">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P341" t="n">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P342" t="n">
@@ -25764,11 +25764,11 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>22291</v>
+        <v>22297</v>
       </c>
       <c r="E343" t="n">
         <v>334</v>
@@ -25807,7 +25807,7 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P343" t="n">
@@ -25882,7 +25882,7 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P344" t="n">
@@ -26019,7 +26019,7 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P346" t="n">
@@ -26094,7 +26094,7 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P347" t="n">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P348" t="n">
@@ -26244,7 +26244,7 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P349" t="n">
@@ -26319,7 +26319,7 @@
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P350" t="n">
@@ -26394,7 +26394,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P351" t="n">
@@ -26469,7 +26469,7 @@
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P352" t="n">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P353" t="n">
@@ -26619,7 +26619,7 @@
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P354" t="n">
@@ -26642,20 +26642,20 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>1730658</v>
+        <v>1730659</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Abdul Rahman.V.P</t>
+          <t>Devarajan.P.T.</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>AINRC</t>
+          <t>BJP</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>22271</v>
+        <v>22263</v>
       </c>
       <c r="E355" t="n">
         <v>1653</v>
@@ -26679,12 +26679,12 @@
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>Abdul Rahman.V.P</t>
+          <t>Devarajan.P.T.</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>AINRC</t>
+          <t>BJP</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -26694,11 +26694,11 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P355" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="Q355" t="b">
         <v>0</v>
@@ -26717,20 +26717,20 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>1730659</v>
+        <v>1730658</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Devarajan.P.T.</t>
+          <t>Abdul Rahman.V.P</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>BJP</t>
+          <t>AINRC</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>22263</v>
+        <v>22271</v>
       </c>
       <c r="E356" t="n">
         <v>1653</v>
@@ -26754,12 +26754,12 @@
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>Devarajan.P.T.</t>
+          <t>Abdul Rahman.V.P</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>BJP</t>
+          <t>AINRC</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -26769,11 +26769,11 @@
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P356" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="Q356" t="b">
         <v>0</v>
@@ -26844,7 +26844,7 @@
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P357" t="n">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P358" t="n">
@@ -27056,7 +27056,7 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P360" t="n">
@@ -27131,7 +27131,7 @@
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P361" t="n">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P362" t="n">
@@ -27281,7 +27281,7 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P363" t="n">
@@ -27356,7 +27356,7 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P364" t="n">
@@ -27431,7 +27431,7 @@
       </c>
       <c r="O365" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P365" t="n">
@@ -27506,7 +27506,7 @@
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P366" t="n">
@@ -27581,7 +27581,7 @@
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P367" t="n">
@@ -27656,7 +27656,7 @@
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P368" t="n">
@@ -27793,7 +27793,7 @@
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P370" t="n">
@@ -27868,7 +27868,7 @@
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P371" t="n">
@@ -27943,7 +27943,7 @@
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P372" t="n">
@@ -28018,7 +28018,7 @@
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P373" t="n">
@@ -28093,7 +28093,7 @@
       </c>
       <c r="O374" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P374" t="n">
@@ -28168,7 +28168,7 @@
       </c>
       <c r="O375" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P375" t="n">
